--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484750_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484750_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.7978</v>
+        <v>6.9977</v>
       </c>
       <c r="E2" t="n">
-        <v>3.121</v>
+        <v>2.4003</v>
       </c>
       <c r="F2" t="n">
-        <v>4.6767</v>
+        <v>4.5974</v>
       </c>
       <c r="G2" t="n">
         <v>5.3372</v>
@@ -610,13 +610,13 @@
         <v>2.8305</v>
       </c>
       <c r="S2" t="n">
-        <v>1.8</v>
+        <v>0.9999</v>
       </c>
       <c r="T2" t="n">
-        <v>1.6359</v>
+        <v>0.9152</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1641</v>
+        <v>0.0847</v>
       </c>
       <c r="V2" t="n">
         <v>0.6606</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. VALERO CHICA</t>
+          <t>J. MERENCIO MORENO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.3415</v>
+        <v>5.6726</v>
       </c>
       <c r="E3" t="n">
-        <v>2.2689</v>
+        <v>1.9497</v>
       </c>
       <c r="F3" t="n">
-        <v>3.0725</v>
+        <v>3.7229</v>
       </c>
       <c r="G3" t="n">
-        <v>1.0343</v>
+        <v>2.1572</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5924</v>
+        <v>1.3547</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4419</v>
+        <v>0.8025</v>
       </c>
       <c r="J3" t="n">
-        <v>0.9394</v>
+        <v>1.3097</v>
       </c>
       <c r="K3" t="n">
-        <v>0.6926</v>
+        <v>1.3735</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2468</v>
+        <v>-0.0638</v>
       </c>
       <c r="M3" t="n">
-        <v>0.095</v>
+        <v>0.8475</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.1001</v>
+        <v>-0.0187</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1951</v>
+        <v>0.8663</v>
       </c>
       <c r="P3" t="n">
-        <v>3.2079</v>
+        <v>1.3209</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-1.887</v>
       </c>
       <c r="R3" t="n">
         <v>3.2079</v>
       </c>
       <c r="S3" t="n">
-        <v>1.0992</v>
+        <v>0.3077</v>
       </c>
       <c r="T3" t="n">
-        <v>1.3296</v>
+        <v>0.0366</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2303</v>
+        <v>0.2711</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.8868</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>2.4904</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-0.6036</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. MERENCIO MORENO</t>
+          <t>J. VALERO CHICA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.7059</v>
+        <v>4.966</v>
       </c>
       <c r="E4" t="n">
-        <v>1.2476</v>
+        <v>1.8406</v>
       </c>
       <c r="F4" t="n">
-        <v>3.4583</v>
+        <v>3.1255</v>
       </c>
       <c r="G4" t="n">
-        <v>2.1572</v>
+        <v>1.0343</v>
       </c>
       <c r="H4" t="n">
-        <v>1.3547</v>
+        <v>0.5924</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8025</v>
+        <v>0.4419</v>
       </c>
       <c r="J4" t="n">
-        <v>1.3097</v>
+        <v>0.9394</v>
       </c>
       <c r="K4" t="n">
-        <v>1.3735</v>
+        <v>0.6926</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.0638</v>
+        <v>0.2468</v>
       </c>
       <c r="M4" t="n">
-        <v>0.8475</v>
+        <v>0.095</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.0187</v>
+        <v>-0.1001</v>
       </c>
       <c r="O4" t="n">
-        <v>0.8663</v>
+        <v>0.1951</v>
       </c>
       <c r="P4" t="n">
-        <v>1.3209</v>
+        <v>3.2079</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.887</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
         <v>3.2079</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.659</v>
+        <v>0.7238</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6655</v>
+        <v>0.9012</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0065</v>
+        <v>-0.1774</v>
       </c>
       <c r="V4" t="n">
-        <v>1.8868</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>2.4904</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.6036</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.8738</v>
+        <v>1.7642</v>
       </c>
       <c r="E5" t="n">
-        <v>1.5993</v>
+        <v>0.8601</v>
       </c>
       <c r="F5" t="n">
-        <v>1.2745</v>
+        <v>0.9041</v>
       </c>
       <c r="G5" t="n">
         <v>0.5986</v>
@@ -844,13 +844,13 @@
         <v>2.8305</v>
       </c>
       <c r="S5" t="n">
-        <v>2.5959</v>
+        <v>1.4864</v>
       </c>
       <c r="T5" t="n">
-        <v>2.1679</v>
+        <v>1.4287</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4281</v>
+        <v>0.0577</v>
       </c>
       <c r="V5" t="n">
         <v>-1.2642</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. TERRADES DAROQUI</t>
+          <t>M. ALONSO ARNEDO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.1873</v>
+        <v>-0.601</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3294</v>
+        <v>0.9606</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.5165999999999999</v>
+        <v>-1.5616</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.8286</v>
+        <v>-0.3473</v>
       </c>
       <c r="H6" t="n">
-        <v>-2.1037</v>
+        <v>-0.583</v>
       </c>
       <c r="I6" t="n">
-        <v>1.275</v>
+        <v>0.2357</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.3403</v>
+        <v>0.3195</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.9658</v>
+        <v>0.3436</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6254999999999999</v>
+        <v>-0.0241</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.4883</v>
+        <v>-0.6667999999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.1379</v>
+        <v>-0.9266</v>
       </c>
       <c r="O6" t="n">
-        <v>0.6496</v>
+        <v>0.2598</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.7548</v>
+        <v>0.1887</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.9435</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>0.1887</v>
       </c>
       <c r="S6" t="n">
-        <v>1.3962</v>
+        <v>0.1802</v>
       </c>
       <c r="T6" t="n">
-        <v>0.368</v>
+        <v>0.0185</v>
       </c>
       <c r="U6" t="n">
-        <v>1.0282</v>
+        <v>0.1617</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-0.6226</v>
       </c>
       <c r="W6" t="n">
-        <v>1.2452</v>
+        <v>0.6226</v>
       </c>
       <c r="X6" t="n">
         <v>-1.2452</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. ALONSO ARNEDO</t>
+          <t>A. TERRADES DAROQUI</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.8929</v>
+        <v>-0.7798</v>
       </c>
       <c r="E7" t="n">
-        <v>0.5893</v>
+        <v>0.116</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.4822</v>
+        <v>-0.8958</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.3473</v>
+        <v>-0.8286</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.583</v>
+        <v>-2.1037</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2357</v>
+        <v>1.275</v>
       </c>
       <c r="J7" t="n">
-        <v>0.3195</v>
+        <v>-0.3403</v>
       </c>
       <c r="K7" t="n">
-        <v>0.3436</v>
+        <v>-0.9658</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.0241</v>
+        <v>0.6254999999999999</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.6667999999999999</v>
+        <v>-0.4883</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.9266</v>
+        <v>-1.1379</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2598</v>
+        <v>0.6496</v>
       </c>
       <c r="P7" t="n">
-        <v>0.1887</v>
+        <v>-0.7548</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-0.9435</v>
       </c>
       <c r="R7" t="n">
         <v>0.1887</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1117</v>
+        <v>0.8036</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3527</v>
+        <v>0.1546</v>
       </c>
       <c r="U7" t="n">
-        <v>0.241</v>
+        <v>0.649</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.6226</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0.6226</v>
+        <v>1.2452</v>
       </c>
       <c r="X7" t="n">
         <v>-1.2452</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D. CALERO BAUTISTA</t>
+          <t>F. GOMEZ CARBONELL</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.5012</v>
+        <v>-1.172</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.4509</v>
+        <v>-3.6883</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.0503</v>
+        <v>2.5163</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.6077</v>
+        <v>-3.2801</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.9407</v>
+        <v>0.6715</v>
       </c>
       <c r="I8" t="n">
-        <v>0.333</v>
+        <v>-3.9515</v>
       </c>
       <c r="J8" t="n">
-        <v>0.3033</v>
+        <v>-4.0575</v>
       </c>
       <c r="K8" t="n">
-        <v>0.36</v>
+        <v>0.349</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.0567</v>
+        <v>-4.4065</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.9109</v>
+        <v>0.7774</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.3007</v>
+        <v>0.3225</v>
       </c>
       <c r="O8" t="n">
-        <v>0.3897</v>
+        <v>0.455</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.1322</v>
+        <v>2.8305</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.887</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.7548</v>
+        <v>2.8305</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2386</v>
+        <v>-0.0998</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1328</v>
+        <v>0.3692</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1058</v>
+        <v>-0.469</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-0.6226</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.6226</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>O. GONZALEZ JURADO</t>
+          <t>D. CALERO BAUTISTA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.2541</v>
+        <v>-1.361</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.7637</v>
+        <v>-1.4694</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.4904</v>
+        <v>0.1084</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.384</v>
+        <v>-0.6077</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.555</v>
+        <v>-0.9407</v>
       </c>
       <c r="I9" t="n">
-        <v>0.171</v>
+        <v>0.333</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.5873</v>
+        <v>0.3033</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.6284</v>
+        <v>0.36</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0411</v>
+        <v>-0.0567</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.7967</v>
+        <v>-0.9109</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.9266</v>
+        <v>-1.3007</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1299</v>
+        <v>0.3897</v>
       </c>
       <c r="P9" t="n">
-        <v>0.1887</v>
+        <v>-1.1322</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-1.887</v>
       </c>
       <c r="R9" t="n">
-        <v>0.1887</v>
+        <v>0.7548</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.4362</v>
+        <v>0.3788</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1764</v>
+        <v>0.1143</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2598</v>
+        <v>0.2645</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.6226</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.6226</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>F. GOMEZ CARBONELL</t>
+          <t>O. GONZALEZ JURADO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,58 +1189,58 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.142</v>
+        <v>-1.9416</v>
       </c>
       <c r="E10" t="n">
-        <v>-5.2086</v>
+        <v>-0.4512</v>
       </c>
       <c r="F10" t="n">
-        <v>2.0666</v>
+        <v>-1.4904</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.2801</v>
+        <v>-1.384</v>
       </c>
       <c r="H10" t="n">
-        <v>0.6715</v>
+        <v>-1.555</v>
       </c>
       <c r="I10" t="n">
-        <v>-3.9515</v>
+        <v>0.171</v>
       </c>
       <c r="J10" t="n">
-        <v>-4.0575</v>
+        <v>-0.5873</v>
       </c>
       <c r="K10" t="n">
-        <v>0.349</v>
+        <v>-0.6284</v>
       </c>
       <c r="L10" t="n">
-        <v>-4.4065</v>
+        <v>0.0411</v>
       </c>
       <c r="M10" t="n">
-        <v>0.7774</v>
+        <v>-0.7967</v>
       </c>
       <c r="N10" t="n">
-        <v>0.3225</v>
+        <v>-0.9266</v>
       </c>
       <c r="O10" t="n">
-        <v>0.455</v>
+        <v>0.1299</v>
       </c>
       <c r="P10" t="n">
-        <v>2.8305</v>
+        <v>0.1887</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2.8305</v>
+        <v>0.1887</v>
       </c>
       <c r="S10" t="n">
-        <v>-2.0698</v>
+        <v>-0.1237</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.1511</v>
+        <v>0.1361</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.9187</v>
+        <v>-0.2598</v>
       </c>
       <c r="V10" t="n">
         <v>-0.6226</v>
@@ -1267,22 +1267,22 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>12.7415</v>
+        <v>13.5451</v>
       </c>
       <c r="E11" t="n">
-        <v>1.7323</v>
+        <v>2.518399999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>11.0091</v>
+        <v>11.0268</v>
       </c>
       <c r="G11" t="n">
         <v>2.6796</v>
       </c>
       <c r="H11" t="n">
-        <v>3.2375</v>
+        <v>3.237500000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.5580000000000003</v>
+        <v>-0.5579999999999998</v>
       </c>
       <c r="J11" t="n">
         <v>2.9174</v>
@@ -1294,16 +1294,16 @@
         <v>-4.673</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.2375000000000002</v>
+        <v>-0.2375000000000003</v>
       </c>
       <c r="N11" t="n">
-        <v>-4.352600000000001</v>
+        <v>-4.3526</v>
       </c>
       <c r="O11" t="n">
         <v>4.1152</v>
       </c>
       <c r="P11" t="n">
-        <v>6.793200000000001</v>
+        <v>6.7932</v>
       </c>
       <c r="Q11" t="n">
         <v>-9.434999999999999</v>
@@ -1312,16 +1312,16 @@
         <v>16.2282</v>
       </c>
       <c r="S11" t="n">
-        <v>3.8532</v>
+        <v>4.656899999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>3.2885</v>
+        <v>4.074400000000001</v>
       </c>
       <c r="U11" t="n">
-        <v>0.5649000000000001</v>
+        <v>0.5825</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.5846000000000002</v>
+        <v>-0.5846</v>
       </c>
       <c r="W11" t="n">
         <v>4.9618</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>3.208</v>
+        <v>3.6289</v>
       </c>
       <c r="E12" t="n">
         <v>2.4925</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7155</v>
+        <v>1.1364</v>
       </c>
       <c r="G12" t="n">
         <v>3.6809</v>
@@ -1390,13 +1390,13 @@
         <v>0.7548</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.9258999999999999</v>
+        <v>-0.505</v>
       </c>
       <c r="T12" t="n">
         <v>-0.5291</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3968</v>
+        <v>0.0241</v>
       </c>
       <c r="V12" t="n">
         <v>-0.3018</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1.4151</v>
+        <v>1.9515</v>
       </c>
       <c r="E13" t="n">
-        <v>0.5590000000000001</v>
+        <v>0.7539</v>
       </c>
       <c r="F13" t="n">
-        <v>0.8561</v>
+        <v>1.1976</v>
       </c>
       <c r="G13" t="n">
         <v>1.1441</v>
@@ -1468,13 +1468,13 @@
         <v>0.7548</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.4838</v>
+        <v>0.0526</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.2228</v>
+        <v>-0.0279</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.261</v>
+        <v>0.0806</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>U. ZAMORA MAÑA</t>
+          <t>T. DESPLACE</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.6339</v>
+        <v>1.0573</v>
       </c>
       <c r="E14" t="n">
-        <v>0.6339</v>
+        <v>1.9263</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>-0.869</v>
       </c>
       <c r="G14" t="n">
-        <v>0.6339</v>
+        <v>-0.7225</v>
       </c>
       <c r="H14" t="n">
-        <v>0.6339</v>
+        <v>-1.7663</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>1.0438</v>
       </c>
       <c r="J14" t="n">
-        <v>0.6339</v>
+        <v>0.2606</v>
       </c>
       <c r="K14" t="n">
-        <v>0.6339</v>
+        <v>0.1698</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>0.09080000000000001</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>-0.9831</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>-1.9361</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>0.953</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>-0.7548</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-1.887</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.1322</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>-0.5784</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>-0.1829</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>-0.3955</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>3.113</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>3.7356</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>-0.6226</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>T. DESPLACE</t>
+          <t>U. ZAMORA MAÑA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4077</v>
+        <v>0.6339</v>
       </c>
       <c r="E15" t="n">
-        <v>1.5365</v>
+        <v>0.6339</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.1288</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.7225</v>
+        <v>0.6339</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.7663</v>
+        <v>0.6339</v>
       </c>
       <c r="I15" t="n">
-        <v>1.0438</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>0.2606</v>
+        <v>0.6339</v>
       </c>
       <c r="K15" t="n">
-        <v>0.1698</v>
+        <v>0.6339</v>
       </c>
       <c r="L15" t="n">
-        <v>0.09080000000000001</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.9831</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.9361</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>0.953</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.7548</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.887</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.1322</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.228</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.5726</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.6554</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>3.113</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>3.7356</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.6226</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. MARZIALI</t>
+          <t>D. CAZORLA ZARAGOZI</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,40 +1657,40 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.2785</v>
+        <v>-0.1459</v>
       </c>
       <c r="E16" t="n">
-        <v>0.5218</v>
+        <v>-0.6203</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.8004</v>
+        <v>0.4744</v>
       </c>
       <c r="G16" t="n">
-        <v>0.4574</v>
+        <v>0.4611</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.3005</v>
+        <v>0.119</v>
       </c>
       <c r="I16" t="n">
-        <v>0.7579</v>
+        <v>0.3421</v>
       </c>
       <c r="J16" t="n">
-        <v>-1.1927</v>
+        <v>0.5617</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.5432</v>
+        <v>1.8438</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.6496</v>
+        <v>-1.2821</v>
       </c>
       <c r="M16" t="n">
-        <v>1.6501</v>
+        <v>-0.1006</v>
       </c>
       <c r="N16" t="n">
-        <v>0.2426</v>
+        <v>-1.7248</v>
       </c>
       <c r="O16" t="n">
-        <v>1.4075</v>
+        <v>1.6242</v>
       </c>
       <c r="P16" t="n">
         <v>-0.9435</v>
@@ -1702,22 +1702,22 @@
         <v>0.9435</v>
       </c>
       <c r="S16" t="n">
-        <v>1.151</v>
+        <v>-0.9087</v>
       </c>
       <c r="T16" t="n">
-        <v>1.4319</v>
+        <v>-0.5402</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2809</v>
+        <v>-0.3685</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.9434</v>
+        <v>1.2452</v>
       </c>
       <c r="W16" t="n">
-        <v>2.1696</v>
+        <v>1.2452</v>
       </c>
       <c r="X16" t="n">
-        <v>-3.113</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1735,10 +1735,10 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.5103</v>
+        <v>-0.3155</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.0764</v>
+        <v>0.1184</v>
       </c>
       <c r="F17" t="n">
         <v>-0.4339</v>
@@ -1780,10 +1780,10 @@
         <v>0.1887</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.5073</v>
+        <v>-0.3124</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1176</v>
+        <v>0.07729999999999999</v>
       </c>
       <c r="U17" t="n">
         <v>-0.3897</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.8577</v>
+        <v>-0.545</v>
       </c>
       <c r="E18" t="n">
         <v>1.1138</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.9715</v>
+        <v>-1.6588</v>
       </c>
       <c r="G18" t="n">
         <v>-1.4714</v>
@@ -1858,13 +1858,13 @@
         <v>0.7548</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.1411</v>
+        <v>0.1716</v>
       </c>
       <c r="T18" t="n">
         <v>0.5472</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.6883</v>
+        <v>-0.3756</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,10 +1891,10 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.1011</v>
+        <v>-0.9063</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.6672</v>
+        <v>-0.4724</v>
       </c>
       <c r="F19" t="n">
         <v>-0.4339</v>
@@ -1936,10 +1936,10 @@
         <v>0.1887</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.4485</v>
+        <v>-0.2537</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.0588</v>
+        <v>0.1361</v>
       </c>
       <c r="U19" t="n">
         <v>-0.3897</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>D. CAZORLA ZARAGOZI</t>
+          <t>M. MARZIALI</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,40 +1969,40 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.4846</v>
+        <v>-1.1944</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.3023</v>
+        <v>-0.6474</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.1823</v>
+        <v>-0.547</v>
       </c>
       <c r="G20" t="n">
-        <v>0.4611</v>
+        <v>0.4574</v>
       </c>
       <c r="H20" t="n">
-        <v>0.119</v>
+        <v>-0.3005</v>
       </c>
       <c r="I20" t="n">
-        <v>0.3421</v>
+        <v>0.7579</v>
       </c>
       <c r="J20" t="n">
-        <v>0.5617</v>
+        <v>-1.1927</v>
       </c>
       <c r="K20" t="n">
-        <v>1.8438</v>
+        <v>-0.5432</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.2821</v>
+        <v>-0.6496</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.1006</v>
+        <v>1.6501</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.7248</v>
+        <v>0.2426</v>
       </c>
       <c r="O20" t="n">
-        <v>1.6242</v>
+        <v>1.4075</v>
       </c>
       <c r="P20" t="n">
         <v>-0.9435</v>
@@ -2014,22 +2014,22 @@
         <v>0.9435</v>
       </c>
       <c r="S20" t="n">
-        <v>-2.2473</v>
+        <v>0.2352</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.2222</v>
+        <v>0.2627</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.0251</v>
+        <v>-0.0276</v>
       </c>
       <c r="V20" t="n">
-        <v>1.2452</v>
+        <v>-0.9434</v>
       </c>
       <c r="W20" t="n">
-        <v>1.2452</v>
+        <v>2.1696</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-3.113</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.5679</v>
+        <v>-3.7976</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.3204</v>
+        <v>-3.8076</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.2475</v>
+        <v>0.01</v>
       </c>
       <c r="G21" t="n">
         <v>-1.5071</v>
@@ -2092,13 +2092,13 @@
         <v>1.5096</v>
       </c>
       <c r="S21" t="n">
-        <v>0.5244</v>
+        <v>0.2947</v>
       </c>
       <c r="T21" t="n">
-        <v>0.7853</v>
+        <v>0.2981</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2609</v>
+        <v>-0.0034</v>
       </c>
       <c r="V21" t="n">
         <v>-0.3208</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>R. AGBEKO</t>
+          <t>A. KLEINJAN RODRIGUEZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.1234</v>
+        <v>-5.2357</v>
       </c>
       <c r="E22" t="n">
-        <v>-5.8626</v>
+        <v>-6.8482</v>
       </c>
       <c r="F22" t="n">
-        <v>1.7392</v>
+        <v>1.6125</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.6457</v>
+        <v>-2.3848</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.3494</v>
+        <v>-0.2199</v>
       </c>
       <c r="I22" t="n">
-        <v>0.7037</v>
+        <v>-2.1648</v>
       </c>
       <c r="J22" t="n">
-        <v>-2.609</v>
+        <v>-2.1013</v>
       </c>
       <c r="K22" t="n">
-        <v>-2.5764</v>
+        <v>0.4969</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.0326</v>
+        <v>-2.5982</v>
       </c>
       <c r="M22" t="n">
-        <v>0.9633</v>
+        <v>-0.2834</v>
       </c>
       <c r="N22" t="n">
-        <v>0.227</v>
+        <v>-0.7168</v>
       </c>
       <c r="O22" t="n">
-        <v>0.7363</v>
+        <v>0.4334</v>
       </c>
       <c r="P22" t="n">
-        <v>-3.2079</v>
+        <v>-2.2644</v>
       </c>
       <c r="Q22" t="n">
         <v>-3.774</v>
       </c>
       <c r="R22" t="n">
-        <v>0.5661</v>
+        <v>1.5096</v>
       </c>
       <c r="S22" t="n">
-        <v>2.2962</v>
+        <v>0.055</v>
       </c>
       <c r="T22" t="n">
-        <v>0.8411999999999999</v>
+        <v>-0.3313</v>
       </c>
       <c r="U22" t="n">
-        <v>1.455</v>
+        <v>0.3863</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.566</v>
+        <v>-0.6415999999999999</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.3208</v>
+        <v>-0.6415999999999999</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.2452</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A. KLEINJAN RODRIGUEZ</t>
+          <t>R. AGBEKO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.818</v>
+        <v>-5.5726</v>
       </c>
       <c r="E23" t="n">
-        <v>-7.4328</v>
+        <v>-6.5446</v>
       </c>
       <c r="F23" t="n">
-        <v>1.6148</v>
+        <v>0.9721</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.3848</v>
+        <v>-1.6457</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.2199</v>
+        <v>-2.3494</v>
       </c>
       <c r="I23" t="n">
-        <v>-2.1648</v>
+        <v>0.7037</v>
       </c>
       <c r="J23" t="n">
-        <v>-2.1013</v>
+        <v>-2.609</v>
       </c>
       <c r="K23" t="n">
-        <v>0.4969</v>
+        <v>-2.5764</v>
       </c>
       <c r="L23" t="n">
-        <v>-2.5982</v>
+        <v>-0.0326</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.2834</v>
+        <v>0.9633</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.7168</v>
+        <v>0.227</v>
       </c>
       <c r="O23" t="n">
-        <v>0.4334</v>
+        <v>0.7363</v>
       </c>
       <c r="P23" t="n">
-        <v>-2.2644</v>
+        <v>-3.2079</v>
       </c>
       <c r="Q23" t="n">
         <v>-3.774</v>
       </c>
       <c r="R23" t="n">
-        <v>1.5096</v>
+        <v>0.5661</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.5273</v>
+        <v>0.847</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.9159</v>
+        <v>0.1591</v>
       </c>
       <c r="U23" t="n">
-        <v>0.3887</v>
+        <v>0.6879</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.6415999999999999</v>
+        <v>-1.566</v>
       </c>
       <c r="W23" t="n">
-        <v>-0.6415999999999999</v>
+        <v>-0.3208</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-1.2452</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-12.0768</v>
+        <v>-10.4414</v>
       </c>
       <c r="E24" t="n">
-        <v>-11.8042</v>
+        <v>-11.9017</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.2727000000000004</v>
+        <v>1.4604</v>
       </c>
       <c r="G24" t="n">
         <v>-2.3871</v>
@@ -2296,7 +2296,7 @@
         <v>-3.193700000000001</v>
       </c>
       <c r="I24" t="n">
-        <v>0.8066</v>
+        <v>0.8065999999999995</v>
       </c>
       <c r="J24" t="n">
         <v>-0.3342000000000009</v>
@@ -2308,13 +2308,13 @@
         <v>-4.3057</v>
       </c>
       <c r="M24" t="n">
-        <v>-2.0529</v>
+        <v>-2.052899999999999</v>
       </c>
       <c r="N24" t="n">
         <v>-7.1652</v>
       </c>
       <c r="O24" t="n">
-        <v>5.1123</v>
+        <v>5.112299999999999</v>
       </c>
       <c r="P24" t="n">
         <v>-7.736700000000001</v>
@@ -2326,19 +2326,19 @@
         <v>9.246300000000002</v>
       </c>
       <c r="S24" t="n">
-        <v>-2.5376</v>
+        <v>-0.9021000000000003</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.0334000000000001</v>
+        <v>-0.1309000000000001</v>
       </c>
       <c r="U24" t="n">
-        <v>-2.5041</v>
+        <v>-0.7711000000000001</v>
       </c>
       <c r="V24" t="n">
         <v>0.5846000000000002</v>
       </c>
       <c r="W24" t="n">
-        <v>5.546399999999998</v>
+        <v>5.5464</v>
       </c>
       <c r="X24" t="n">
         <v>-4.9618</v>
